--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N41_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N41_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>61.83560164768426</v>
+        <v>10.04828526774869</v>
       </c>
       <c r="D2" t="n">
-        <v>61.54841169399536</v>
+        <v>10.00161690027424</v>
       </c>
       <c r="E2" t="n">
-        <v>18.59950700312291</v>
+        <v>3.022419888007474</v>
       </c>
       <c r="F2" t="n">
-        <v>18.60696175210303</v>
+        <v>3.023631284716742</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.20876082384295</v>
+        <v>2.796423633874479</v>
       </c>
       <c r="D3" t="n">
-        <v>16.90679082595841</v>
+        <v>2.747353509218242</v>
       </c>
       <c r="E3" t="n">
-        <v>18.59950700312291</v>
+        <v>3.022419888007474</v>
       </c>
       <c r="F3" t="n">
-        <v>18.60696175210303</v>
+        <v>3.023631284716742</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.67752217573655</v>
+        <v>2.710097353557189</v>
       </c>
       <c r="D4" t="n">
-        <v>16.57299167137155</v>
+        <v>2.693111146597877</v>
       </c>
       <c r="E4" t="n">
-        <v>18.59950700312291</v>
+        <v>3.022419888007474</v>
       </c>
       <c r="F4" t="n">
-        <v>18.60696175210303</v>
+        <v>3.023631284716742</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>59.8708945876909</v>
+        <v>9.729020370499772</v>
       </c>
       <c r="D5" t="n">
-        <v>59.52919464485702</v>
+        <v>9.673494129789267</v>
       </c>
       <c r="E5" t="n">
-        <v>18.59950700312291</v>
+        <v>3.022419888007474</v>
       </c>
       <c r="F5" t="n">
-        <v>18.60696175210303</v>
+        <v>3.023631284716742</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>52.40492613215098</v>
+        <v>8.515800496474535</v>
       </c>
       <c r="D6" t="n">
-        <v>52.31167899490392</v>
+        <v>8.500647836671888</v>
       </c>
       <c r="E6" t="n">
-        <v>18.59950700312291</v>
+        <v>3.022419888007474</v>
       </c>
       <c r="F6" t="n">
-        <v>18.60696175210303</v>
+        <v>3.023631284716742</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>12.77038110880701</v>
+        <v>2.075186930181139</v>
       </c>
       <c r="D7" t="n">
-        <v>12.49885300547404</v>
+        <v>2.031063613389532</v>
       </c>
       <c r="E7" t="n">
-        <v>18.59950700312291</v>
+        <v>3.022419888007474</v>
       </c>
       <c r="F7" t="n">
-        <v>18.60696175210303</v>
+        <v>3.023631284716742</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>36.26048289243143</v>
+        <v>5.892328470020107</v>
       </c>
       <c r="D8" t="n">
-        <v>35.99582667653759</v>
+        <v>5.849321834937358</v>
       </c>
       <c r="E8" t="n">
-        <v>18.59950700312291</v>
+        <v>3.022419888007474</v>
       </c>
       <c r="F8" t="n">
-        <v>18.60696175210303</v>
+        <v>3.023631284716742</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>9.110872381346182</v>
+        <v>1.480516761968755</v>
       </c>
       <c r="D9" t="n">
-        <v>8.94677623343137</v>
+        <v>1.453851137932598</v>
       </c>
       <c r="E9" t="n">
-        <v>18.59950700312291</v>
+        <v>3.022419888007474</v>
       </c>
       <c r="F9" t="n">
-        <v>18.60696175210303</v>
+        <v>3.023631284716742</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>33.30806687286341</v>
+        <v>5.412560866840304</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59641137282977</v>
+        <v>5.459416848084838</v>
       </c>
       <c r="E10" t="n">
-        <v>18.59950700312291</v>
+        <v>3.022419888007474</v>
       </c>
       <c r="F10" t="n">
-        <v>18.60696175210303</v>
+        <v>3.023631284716742</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>40.65350932466882</v>
+        <v>6.606195265258683</v>
       </c>
       <c r="D11" t="n">
-        <v>40.94738611559251</v>
+        <v>6.653950243783783</v>
       </c>
       <c r="E11" t="n">
-        <v>18.59950700312291</v>
+        <v>3.022419888007474</v>
       </c>
       <c r="F11" t="n">
-        <v>18.60696175210303</v>
+        <v>3.023631284716742</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>52.65827097338473</v>
+        <v>8.556969033175019</v>
       </c>
       <c r="D12" t="n">
-        <v>52.5034393570085</v>
+        <v>8.531808895513882</v>
       </c>
       <c r="E12" t="n">
-        <v>18.59950700312291</v>
+        <v>3.022419888007474</v>
       </c>
       <c r="F12" t="n">
-        <v>18.60696175210303</v>
+        <v>3.023631284716742</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>38.69843475005957</v>
+        <v>6.28849564688468</v>
       </c>
       <c r="D13" t="n">
-        <v>39.0362279353673</v>
+        <v>6.343387039497187</v>
       </c>
       <c r="E13" t="n">
-        <v>18.59950700312291</v>
+        <v>3.022419888007474</v>
       </c>
       <c r="F13" t="n">
-        <v>18.60696175210303</v>
+        <v>3.023631284716742</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>55.13884487813792</v>
+        <v>8.960062292697412</v>
       </c>
       <c r="D14" t="n">
-        <v>55.46276906037892</v>
+        <v>9.012699972311575</v>
       </c>
       <c r="E14" t="n">
-        <v>18.59950700312291</v>
+        <v>3.022419888007474</v>
       </c>
       <c r="F14" t="n">
-        <v>18.60696175210303</v>
+        <v>3.023631284716742</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>43.6719247618034</v>
+        <v>7.096687773793052</v>
       </c>
       <c r="D15" t="n">
-        <v>43.61149058545977</v>
+        <v>7.086867220137213</v>
       </c>
       <c r="E15" t="n">
-        <v>18.59950700312291</v>
+        <v>3.022419888007474</v>
       </c>
       <c r="F15" t="n">
-        <v>18.60696175210303</v>
+        <v>3.023631284716742</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>29.81816612187949</v>
+        <v>4.845451994805417</v>
       </c>
       <c r="D16" t="n">
-        <v>30.0348014652111</v>
+        <v>4.880655238096804</v>
       </c>
       <c r="E16" t="n">
-        <v>18.59950700312291</v>
+        <v>3.022419888007474</v>
       </c>
       <c r="F16" t="n">
-        <v>18.60696175210303</v>
+        <v>3.023631284716742</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>50.58556954104338</v>
+        <v>8.22015505041955</v>
       </c>
       <c r="D17" t="n">
-        <v>50.34171784049834</v>
+        <v>8.18052914908098</v>
       </c>
       <c r="E17" t="n">
-        <v>18.59950700312291</v>
+        <v>3.022419888007474</v>
       </c>
       <c r="F17" t="n">
-        <v>18.60696175210303</v>
+        <v>3.023631284716742</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>55.96506977553879</v>
+        <v>9.094323838525053</v>
       </c>
       <c r="D18" t="n">
-        <v>55.65395867802989</v>
+        <v>9.043768285179857</v>
       </c>
       <c r="E18" t="n">
-        <v>18.59950700312291</v>
+        <v>3.022419888007474</v>
       </c>
       <c r="F18" t="n">
-        <v>18.60696175210303</v>
+        <v>3.023631284716742</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>78.05939758898496</v>
+        <v>12.68465210821006</v>
       </c>
       <c r="D19" t="n">
-        <v>78.37756855158059</v>
+        <v>12.73635488963185</v>
       </c>
       <c r="E19" t="n">
-        <v>18.59950700312291</v>
+        <v>3.022419888007474</v>
       </c>
       <c r="F19" t="n">
-        <v>18.60696175210303</v>
+        <v>3.023631284716742</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>67.62847771351969</v>
+        <v>10.98962762844695</v>
       </c>
       <c r="D20" t="n">
-        <v>67.29333137186191</v>
+        <v>10.93516634792756</v>
       </c>
       <c r="E20" t="n">
-        <v>18.59950700312291</v>
+        <v>3.022419888007474</v>
       </c>
       <c r="F20" t="n">
-        <v>18.60696175210303</v>
+        <v>3.023631284716742</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>54.55015733810083</v>
+        <v>8.864400567441386</v>
       </c>
       <c r="D21" t="n">
-        <v>54.19789075369901</v>
+        <v>8.80715724747609</v>
       </c>
       <c r="E21" t="n">
-        <v>18.59950700312291</v>
+        <v>3.022419888007474</v>
       </c>
       <c r="F21" t="n">
-        <v>18.60696175210303</v>
+        <v>3.023631284716742</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
